--- a/inputs/A2_Extra_Inputs/A-Xtra_Battery_Replacement.xlsx
+++ b/inputs/A2_Extra_Inputs/A-Xtra_Battery_Replacement.xlsx
@@ -1519,8 +1519,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000F48F53D8446FB4EB61FD3AFE2640F25" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c42e2caa13ae5d6057eea9be68815fce">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7db9c71a-8f0f-4486-8c92-6242e053eab7" xmlns:ns3="8ae01698-3168-4e7f-b9e7-0ddc1c80de73" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b95e89a8284191eba76f4506755f34ad" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000F48F53D8446FB4EB61FD3AFE2640F25" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="83cf53e23258b582a307689f9bad4776">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7db9c71a-8f0f-4486-8c92-6242e053eab7" xmlns:ns3="8ae01698-3168-4e7f-b9e7-0ddc1c80de73" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8e6c764710efd91b3147b7c3b8958216" ns2:_="" ns3:_="">
     <xsd:import namespace="7db9c71a-8f0f-4486-8c92-6242e053eab7"/>
     <xsd:import namespace="8ae01698-3168-4e7f-b9e7-0ddc1c80de73"/>
     <xsd:element name="properties">
@@ -1728,7 +1728,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7DE09ED-C3B7-414D-85BD-0360FE29A6AE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E5222A4-3EC3-43D4-A8D7-918601754226}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
